--- a/Deliverables/GC EA assessment tool - categories template.xlsx
+++ b/Deliverables/GC EA assessment tool - categories template.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +113,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B6B6B"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="16">
@@ -219,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -303,6 +309,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -670,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B30"/>
+  <dimension ref="B1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -724,21 +733,21 @@
     <row r="9" ht="17.6" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1.  Click a cell in the Categories column. A dropdown appears.</t>
+          <t>1.  Click a cell under "Also about". A dropdown appears with the five categories.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2.  Choose the entry that matches. The list holds each category on its own and the combinations anybody is likely to need.</t>
+          <t>2.  Pick one. If the question is about a second thing, use the next column, and the one after that for a third. Four questions out of 176 need all three.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3.  Leave it empty when the question is only about its own domain. That is the normal case: about three quarters of them.</t>
+          <t>3.  Leave them empty when the question is only about its own domain. That is the normal case: 130 of the 176.</t>
         </is>
       </c>
     </row>
@@ -746,88 +755,96 @@
     <row r="13" ht="60" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>If you need a combination the list does not hold, type it, separated by commas. The tool checks every name when it reads this file and refuses the whole import if one is not recognised, naming the question it was in. A category nobody recognises would otherwise score nothing, on every screen, and never be noticed.</t>
+          <t>Three columns and not one because neither Google Sheets nor Excel has a dropdown you can pick more than one thing from. Putting the combinations into a single list does not work either: a dropdown list is itself comma separated, so "Security, Privacy" splits into two entries. Three columns sharing one list is the shape that works with nothing typed, and nothing typed means nothing mistyped.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="8" customHeight="1"/>
-    <row r="15" ht="22.4" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="15" ht="45" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>If you do type into these cells, the tool checks every name when it reads this file and refuses the whole import if one is not recognised, naming the question it was in. A category nobody recognises would otherwise score nothing, on every screen, and never be noticed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="8" customHeight="1"/>
+    <row r="17" ht="22.4" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>The nine categories</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Four are the domains themselves, filled in by the tab a question is on: Business, Data, Application, Technology.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Five are what the Categories column asks for: Security, Privacy, Financial, Accessibility, Official Languages.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="8" customHeight="1"/>
-    <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="45" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>A question can carry as many as apply. It still counts once in the overall score, through its domain, and at full weight inside every category it carries. So the category scores do not add up to the overall, and the tool says so.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="22.4" customHeight="1">
-      <c r="B21" s="5" t="inlineStr">
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23" ht="22.4" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Never duplicate a question onto a second tab</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>A question that appears on two tabs is counted twice in the overall score, and the department’s number moves because of how we filed a question. One question, one tab, as many categories as apply.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="8" customHeight="1"/>
-    <row r="24" ht="22.4" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="22.4" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Two categories rest on very little</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Accessibility is asked about by three questions and Official Languages by two. That is thin, and it is worth knowing before anybody reads a score for either: a number built on two questions moves a long way on one answer. If there should be more, that is a gap in the instrument and not in this column.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="8" customHeight="1"/>
-    <row r="27" ht="45" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="45" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>An earlier version of this workbook said both were empty. That was wrong. Six questions mention something "accessible" and three of them are about accessibility; the other three are the FAIR principles’ Accessible and data reaching other departments, which is a different sense of the word.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="22.4" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="22.4" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>The Answer type column</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Ten of the 176 questions read as yes or no rather than as a maturity, which you named yourself. The Answer type column says which we think each one is, and the Answer column beside it offers the matching picker: 0 to 10 for a scale question, Yes and No for the others, and N/A on both. Our reading is provisional; change the type and the picker follows.</t>
         </is>
@@ -844,17 +861,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -889,25 +908,35 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Also about</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and </t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Answer type</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Maturity Label</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -937,14 +966,16 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -959,14 +990,16 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -981,14 +1014,16 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -1003,14 +1038,16 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -1025,14 +1062,16 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -1047,14 +1086,16 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -1069,14 +1110,16 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -1091,14 +1134,16 @@
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -1113,14 +1158,16 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr"/>
@@ -1135,14 +1182,16 @@
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr"/>
@@ -1157,14 +1206,16 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -1179,14 +1230,16 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -1201,14 +1254,16 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -1223,14 +1278,16 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -1256,14 +1313,16 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -1278,14 +1337,16 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -1300,14 +1361,16 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -1322,14 +1385,16 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -1344,14 +1409,16 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -1366,14 +1433,16 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -1388,14 +1457,16 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -1410,14 +1481,16 @@
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -1432,14 +1505,16 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -1454,14 +1529,16 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -1476,14 +1553,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -1498,14 +1577,16 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -1520,14 +1601,16 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -1553,14 +1636,16 @@
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -1575,14 +1660,16 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -1597,14 +1684,16 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -1619,14 +1708,16 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -1641,14 +1732,16 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -1663,14 +1756,16 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -1685,14 +1780,16 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr"/>
@@ -1707,14 +1804,16 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -1729,14 +1828,16 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
@@ -1762,14 +1863,16 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -1784,14 +1887,16 @@
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -1806,14 +1911,16 @@
         </is>
       </c>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -1828,14 +1935,16 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H47" s="15" t="n"/>
+      <c r="I47" s="15" t="n"/>
+      <c r="J47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr"/>
@@ -1850,14 +1959,16 @@
         </is>
       </c>
       <c r="D48" s="13" t="n"/>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="n"/>
-      <c r="G48" s="15" t="n"/>
+      <c r="E48" s="13" t="n"/>
+      <c r="F48" s="13" t="n"/>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H48" s="15" t="n"/>
+      <c r="I48" s="15" t="n"/>
+      <c r="J48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr"/>
@@ -1872,14 +1983,16 @@
         </is>
       </c>
       <c r="D49" s="13" t="n"/>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
+      <c r="E49" s="13" t="n"/>
+      <c r="F49" s="13" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H49" s="15" t="n"/>
+      <c r="I49" s="15" t="n"/>
+      <c r="J49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr"/>
@@ -1894,14 +2007,16 @@
         </is>
       </c>
       <c r="D50" s="13" t="n"/>
-      <c r="E50" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F50" s="15" t="n"/>
-      <c r="G50" s="15" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H50" s="15" t="n"/>
+      <c r="I50" s="15" t="n"/>
+      <c r="J50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr"/>
@@ -1916,14 +2031,16 @@
         </is>
       </c>
       <c r="D51" s="13" t="n"/>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="n"/>
-      <c r="G51" s="15" t="n"/>
+      <c r="E51" s="13" t="n"/>
+      <c r="F51" s="13" t="n"/>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H51" s="15" t="n"/>
+      <c r="I51" s="15" t="n"/>
+      <c r="J51" s="15" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
@@ -1949,14 +2066,16 @@
         </is>
       </c>
       <c r="D53" s="13" t="n"/>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="13" t="n"/>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H53" s="15" t="n"/>
+      <c r="I53" s="15" t="n"/>
+      <c r="J53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr"/>
@@ -1971,14 +2090,16 @@
         </is>
       </c>
       <c r="D54" s="13" t="n"/>
-      <c r="E54" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="13" t="n"/>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H54" s="15" t="n"/>
+      <c r="I54" s="15" t="n"/>
+      <c r="J54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr"/>
@@ -1993,14 +2114,16 @@
         </is>
       </c>
       <c r="D55" s="13" t="n"/>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="n"/>
-      <c r="G55" s="15" t="n"/>
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="13" t="n"/>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H55" s="15" t="n"/>
+      <c r="I55" s="15" t="n"/>
+      <c r="J55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr"/>
@@ -2015,14 +2138,16 @@
         </is>
       </c>
       <c r="D56" s="13" t="n"/>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F56" s="15" t="n"/>
-      <c r="G56" s="15" t="n"/>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="13" t="n"/>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H56" s="15" t="n"/>
+      <c r="I56" s="15" t="n"/>
+      <c r="J56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr"/>
@@ -2037,14 +2162,16 @@
         </is>
       </c>
       <c r="D57" s="13" t="n"/>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="n"/>
-      <c r="G57" s="15" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H57" s="15" t="n"/>
+      <c r="I57" s="15" t="n"/>
+      <c r="J57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr"/>
@@ -2059,14 +2186,16 @@
         </is>
       </c>
       <c r="D58" s="13" t="n"/>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F58" s="15" t="n"/>
-      <c r="G58" s="15" t="n"/>
       <c r="H58" s="15" t="n"/>
+      <c r="I58" s="15" t="n"/>
+      <c r="J58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr"/>
@@ -2081,14 +2210,16 @@
         </is>
       </c>
       <c r="D59" s="13" t="n"/>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="n"/>
-      <c r="G59" s="15" t="n"/>
+      <c r="E59" s="13" t="n"/>
+      <c r="F59" s="13" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H59" s="15" t="n"/>
+      <c r="I59" s="15" t="n"/>
+      <c r="J59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr"/>
@@ -2103,14 +2234,16 @@
         </is>
       </c>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H60" s="15" t="n"/>
+      <c r="I60" s="15" t="n"/>
+      <c r="J60" s="15" t="n"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
@@ -2136,14 +2269,16 @@
         </is>
       </c>
       <c r="D62" s="13" t="n"/>
-      <c r="E62" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F62" s="15" t="n"/>
-      <c r="G62" s="15" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H62" s="15" t="n"/>
+      <c r="I62" s="15" t="n"/>
+      <c r="J62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr"/>
@@ -2158,14 +2293,16 @@
         </is>
       </c>
       <c r="D63" s="13" t="n"/>
-      <c r="E63" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="n"/>
-      <c r="G63" s="15" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="13" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H63" s="15" t="n"/>
+      <c r="I63" s="15" t="n"/>
+      <c r="J63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr"/>
@@ -2180,14 +2317,16 @@
         </is>
       </c>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="13" t="n"/>
+      <c r="F64" s="13" t="n"/>
+      <c r="G64" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F64" s="15" t="n"/>
-      <c r="G64" s="15" t="n"/>
       <c r="H64" s="15" t="n"/>
+      <c r="I64" s="15" t="n"/>
+      <c r="J64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr"/>
@@ -2202,14 +2341,16 @@
         </is>
       </c>
       <c r="D65" s="13" t="n"/>
-      <c r="E65" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="n"/>
-      <c r="G65" s="15" t="n"/>
+      <c r="E65" s="13" t="n"/>
+      <c r="F65" s="13" t="n"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H65" s="15" t="n"/>
+      <c r="I65" s="15" t="n"/>
+      <c r="J65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr"/>
@@ -2224,14 +2365,16 @@
         </is>
       </c>
       <c r="D66" s="13" t="n"/>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="n"/>
-      <c r="G66" s="15" t="n"/>
+      <c r="E66" s="13" t="n"/>
+      <c r="F66" s="13" t="n"/>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H66" s="15" t="n"/>
+      <c r="I66" s="15" t="n"/>
+      <c r="J66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr"/>
@@ -2246,14 +2389,16 @@
         </is>
       </c>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E67" s="13" t="n"/>
+      <c r="F67" s="13" t="n"/>
+      <c r="G67" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F67" s="15" t="n"/>
-      <c r="G67" s="15" t="n"/>
       <c r="H67" s="15" t="n"/>
+      <c r="I67" s="15" t="n"/>
+      <c r="J67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr"/>
@@ -2268,14 +2413,16 @@
         </is>
       </c>
       <c r="D68" s="13" t="n"/>
-      <c r="E68" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F68" s="15" t="n"/>
-      <c r="G68" s="15" t="n"/>
+      <c r="E68" s="13" t="n"/>
+      <c r="F68" s="13" t="n"/>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H68" s="15" t="n"/>
+      <c r="I68" s="15" t="n"/>
+      <c r="J68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr"/>
@@ -2290,14 +2437,16 @@
         </is>
       </c>
       <c r="D69" s="13" t="n"/>
-      <c r="E69" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
+      <c r="E69" s="13" t="n"/>
+      <c r="F69" s="13" t="n"/>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H69" s="15" t="n"/>
+      <c r="I69" s="15" t="n"/>
+      <c r="J69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr"/>
@@ -2312,37 +2461,45 @@
         </is>
       </c>
       <c r="D70" s="13" t="n"/>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="n"/>
-      <c r="G70" s="15" t="n"/>
+      <c r="E70" s="13" t="n"/>
+      <c r="F70" s="13" t="n"/>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H70" s="15" t="n"/>
+      <c r="I70" s="15" t="n"/>
+      <c r="J70" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="Pick the subjects this question is also about, beyond its own domain. Leave it empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages,Security, Privacy,Security, Financial,Privacy, Financial,Accessibility, Official Languages,Privacy, Accessibility, Official Languages,Security, Privacy, Financial"</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F34 F35 F36 F37 F38 F39 F40 F41 F42 F44 F45 F46 F47 F48 F49 F50 F51 F53 F54 F55 F56 F57 F59 F60 F62 F63 F65 F66 F68 F69 F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H34 H35 H36 H37 H38 H39 H40 H41 H42 H44 H45 H46 H47 H48 H49 H50 H51 H53 H54 H55 H56 H57 H59 H60 H62 H63 H65 H66 H68 H69 H70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F58 F64 F67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H58 H64 H67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2356,17 +2513,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2401,25 +2560,35 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Also about</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and </t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Answer type</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Maturity Label</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -2449,14 +2618,16 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -2471,14 +2642,16 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -2493,14 +2666,16 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -2515,14 +2690,16 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -2537,14 +2714,16 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -2559,14 +2738,16 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -2581,14 +2762,16 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -2603,14 +2786,16 @@
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -2625,14 +2810,16 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -2658,14 +2845,16 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -2680,14 +2869,16 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -2702,14 +2893,16 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -2724,14 +2917,16 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -2746,14 +2941,16 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -2768,14 +2965,16 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -2790,14 +2989,16 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -2812,14 +3013,16 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -2834,14 +3037,16 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -2856,14 +3061,16 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -2878,14 +3085,16 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -2900,14 +3109,16 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -2933,14 +3144,16 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -2955,14 +3168,16 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -2977,14 +3192,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -2999,14 +3216,16 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -3021,14 +3240,16 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -3043,14 +3264,16 @@
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
@@ -3065,14 +3288,16 @@
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -3087,14 +3312,16 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -3109,14 +3336,16 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
@@ -3142,14 +3371,16 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -3164,14 +3395,16 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -3186,14 +3419,16 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
@@ -3219,14 +3454,16 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -3241,14 +3478,16 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -3263,14 +3502,16 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -3285,14 +3526,16 @@
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -3307,14 +3550,16 @@
         </is>
       </c>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -3329,36 +3574,44 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H47" s="15" t="n"/>
+      <c r="I47" s="15" t="n"/>
+      <c r="J47" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A41:J41"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="Pick the subjects this question is also about, beyond its own domain. Leave it empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages,Security, Privacy,Security, Financial,Privacy, Financial,Accessibility, Official Languages,Privacy, Accessibility, Official Languages,Security, Privacy, Financial"</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F29 F30 F31 F32 F33 F34 F36 F38 F39 F40 F42 F43 F44 F45 F46 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H29 H30 H31 H32 H33 H34 H36 H38 H39 H40 H42 H43 H44 H45 H46 H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F28 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H28 H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3372,17 +3625,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3417,25 +3672,35 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Also about</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and </t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Answer type</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Maturity Label</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -3465,14 +3730,16 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -3487,14 +3754,16 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -3509,14 +3778,16 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -3531,14 +3802,16 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -3553,14 +3826,16 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -3575,14 +3850,16 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -3597,14 +3874,16 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -3619,14 +3898,16 @@
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -3641,14 +3922,16 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -3674,14 +3957,16 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -3696,14 +3981,16 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -3718,14 +4005,16 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -3740,14 +4029,16 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -3762,14 +4053,16 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -3784,14 +4077,16 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -3806,14 +4101,16 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -3828,14 +4125,16 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -3850,14 +4149,16 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -3872,14 +4173,16 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -3905,14 +4208,16 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -3927,14 +4232,16 @@
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -3949,14 +4256,16 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -3971,14 +4280,16 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -3993,14 +4304,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -4015,14 +4328,16 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -4037,14 +4352,16 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -4059,14 +4376,16 @@
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -4092,14 +4411,16 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -4114,14 +4435,16 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -4136,14 +4459,16 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -4158,14 +4483,16 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -4180,14 +4507,16 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -4202,14 +4531,16 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr"/>
@@ -4224,14 +4555,16 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -4246,14 +4579,16 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -4268,14 +4603,16 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -4290,35 +4627,43 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A25:J25"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="Pick the subjects this question is also about, beyond its own domain. Leave it empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages,Security, Privacy,Security, Financial,Privacy, Financial,Accessibility, Official Languages,Privacy, Accessibility, Official Languages,Security, Privacy, Financial"</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F26 F27 F28 F31 F32 F33 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H26 H27 H28 H31 H32 H33 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H29 H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4332,17 +4677,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4377,25 +4724,35 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Also about</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">and </t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Answer type</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Maturity Label</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -4425,14 +4782,16 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -4447,14 +4806,16 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -4469,14 +4830,16 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -4491,14 +4854,16 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -4513,14 +4878,16 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -4535,14 +4902,16 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -4557,14 +4926,16 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -4590,14 +4961,16 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr"/>
@@ -4612,14 +4985,16 @@
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr"/>
@@ -4634,14 +5009,16 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -4656,14 +5033,16 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -4678,14 +5057,16 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -4700,14 +5081,16 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -4722,14 +5105,16 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -4744,14 +5129,16 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -4766,14 +5153,16 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -4788,14 +5177,16 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -4821,14 +5212,16 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -4843,14 +5236,16 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -4865,14 +5260,16 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -4887,14 +5284,16 @@
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -4909,14 +5308,16 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -4931,14 +5332,16 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -4953,14 +5356,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
@@ -4986,14 +5391,16 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -5008,14 +5415,16 @@
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="13" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
@@ -5030,14 +5439,16 @@
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -5052,14 +5463,16 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -5074,14 +5487,16 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -5096,14 +5511,16 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -5118,14 +5535,16 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -5140,14 +5559,16 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
@@ -5173,14 +5594,16 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -5195,14 +5618,16 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -5217,14 +5642,16 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -5239,14 +5666,16 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -5261,14 +5690,16 @@
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="13" t="n"/>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -5283,14 +5714,16 @@
         </is>
       </c>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -5305,36 +5738,44 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="E47" s="13" t="n"/>
+      <c r="F47" s="13" t="n"/>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
       <c r="H47" s="15" t="n"/>
+      <c r="I47" s="15" t="n"/>
+      <c r="J47" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="Pick the subjects this question is also about, beyond its own domain. Leave it empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages,Security, Privacy,Security, Financial,Privacy, Financial,Accessibility, Official Languages,Privacy, Accessibility, Official Languages,Security, Privacy, Financial"</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F32 F33 F34 F35 F37 F38 F39 F41 F42 F43 F44 F45 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H13 H14 H15 H16 H17 H18 H20 H21 H22 H24 H25 H26 H27 H28 H29 H30 H32 H33 H34 H35 H37 H38 H39 H41 H42 H43 H44 H45 H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="F19 F36 F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="H19 H36 H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5642,7 +6083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5856,6 +6297,13 @@
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="12" t="n"/>
     </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>This tab is your own Summary Dashboard, reproduced so nothing is missing from this copy. It does not calculate here: this workbook is for the Categories columns, and the scoring happens in the tool.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/Deliverables/GC EA assessment tool - categories template.xlsx
+++ b/Deliverables/GC EA assessment tool - categories template.xlsx
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B32"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -733,118 +733,103 @@
     <row r="9" ht="17.6" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1.  Click a cell under "Also about". A dropdown appears with the five categories.</t>
+          <t>1.  Click a cell in the Categories column. A dropdown appears with the five.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2.  Pick one. If the question is about a second thing, use the next column, and the one after that for a third. Four questions out of 176 need all three.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>3.  Leave them empty when the question is only about its own domain. That is the normal case: 130 of the 176.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="8" customHeight="1"/>
-    <row r="13" ht="60" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Three columns and not one because neither Google Sheets nor Excel has a dropdown you can pick more than one thing from. Putting the combinations into a single list does not work either: a dropdown list is itself comma separated, so "Security, Privacy" splits into two entries. Three columns sharing one list is the shape that works with nothing typed, and nothing typed means nothing mistyped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="8" customHeight="1"/>
-    <row r="15" ht="45" customHeight="1">
+          <t>2.  Tick as many as apply. Most questions need none; 130 of the 176 stay empty, which means "this one is only about its own domain".</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="8" customHeight="1"/>
+    <row r="12" ht="45" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>If you do type into these cells instead, the tool checks every name when it reads this file and refuses the whole import if one is not recognised, naming the question it was in. A category nobody recognises would otherwise score nothing, on every screen, and never be noticed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="22.4" customHeight="1">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>The nine categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>If you do type into these cells, the tool checks every name when it reads this file and refuses the whole import if one is not recognised, naming the question it was in. A category nobody recognises would otherwise score nothing, on every screen, and never be noticed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="8" customHeight="1"/>
-    <row r="17" ht="22.4" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>The nine categories</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>Four are the domains themselves, filled in by the tab a question is on: Business, Data, Application, Technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Five are what the Categories column asks for: Security, Privacy, Financial, Accessibility, Official Languages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="45" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Four are the domains themselves, filled in by the tab a question is on: Business, Data, Application, Technology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Five are what the Categories column asks for: Security, Privacy, Financial, Accessibility, Official Languages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="45" customHeight="1">
+          <t>A question can carry as many as apply. It still counts once in the overall score, through its domain, and at full weight inside every category it carries. So the category scores do not add up to the overall, and the tool says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="22.4" customHeight="1">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Never duplicate a question onto a second tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>A question can carry as many as apply. It still counts once in the overall score, through its domain, and at full weight inside every category it carries. So the category scores do not add up to the overall, and the tool says so.</t>
+          <t>A question that appears on two tabs is counted twice in the overall score, and the department’s number moves because of how we filed a question. One question, one tab, as many categories as apply.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1"/>
     <row r="23" ht="22.4" customHeight="1">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Never duplicate a question onto a second tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Two categories rest on very little</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>A question that appears on two tabs is counted twice in the overall score, and the department’s number moves because of how we filed a question. One question, one tab, as many categories as apply.</t>
+          <t>Accessibility is asked about by three questions and Official Languages by two. That is thin, and it is worth knowing before anybody reads a score for either: a number built on two questions moves a long way on one answer. If there should be more, that is a gap in the instrument and not in this column.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="8" customHeight="1"/>
-    <row r="26" ht="22.4" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Two categories rest on very little</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Accessibility is asked about by three questions and Official Languages by two. That is thin, and it is worth knowing before anybody reads a score for either: a number built on two questions moves a long way on one answer. If there should be more, that is a gap in the instrument and not in this column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="45" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>An earlier version of this workbook said both were empty. That was wrong. Six questions mention something "accessible" and three of them are about accessibility; the other three are the FAIR principles’ Accessible and data reaching other departments, which is a different sense of the word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="8" customHeight="1"/>
+    <row r="28" ht="22.4" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>The Answer type column</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>An earlier version of this workbook said both were empty. That was wrong. Six questions mention something "accessible" and three of them are about accessibility; the other three are the FAIR principles’ Accessible and data reaching other departments, which is a different sense of the word.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="22.4" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>The Answer type column</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Ten of the 176 questions read as yes or no rather than as a maturity, which you named yourself. The Answer type column says which we think each one is, and the Answer column beside it offers the matching picker: 0 to 10 for a scale question, Yes and No for the others, and N/A on both. Our reading is provisional; change the type and the picker follows.</t>
         </is>
@@ -861,19 +846,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -908,35 +891,25 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Also about</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Answer type</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">and </t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Answer type</t>
+          <t>Maturity Label</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Maturity Label</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -966,16 +939,14 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -990,16 +961,14 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -1014,16 +983,14 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -1038,16 +1005,14 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -1062,16 +1027,14 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -1086,16 +1049,14 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -1110,16 +1071,14 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -1134,16 +1093,14 @@
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -1158,16 +1115,14 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr"/>
@@ -1182,16 +1137,14 @@
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr"/>
@@ -1206,16 +1159,14 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -1230,16 +1181,14 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -1254,16 +1203,14 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -1278,16 +1225,14 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -1313,16 +1258,14 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -1337,16 +1280,14 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -1361,16 +1302,14 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -1385,16 +1324,14 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -1409,16 +1346,14 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -1433,16 +1368,14 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -1457,16 +1390,14 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -1481,16 +1412,14 @@
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -1505,16 +1434,14 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -1529,16 +1456,14 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -1553,16 +1478,14 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -1577,16 +1500,14 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -1601,16 +1522,14 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -1636,16 +1555,14 @@
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -1660,16 +1577,14 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -1684,16 +1599,14 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -1708,16 +1621,14 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
       <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -1732,16 +1643,14 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -1756,16 +1665,14 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -1780,16 +1687,14 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr"/>
@@ -1804,16 +1709,14 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -1828,16 +1731,14 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
@@ -1863,16 +1764,14 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -1887,16 +1786,14 @@
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -1911,16 +1808,14 @@
         </is>
       </c>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -1935,16 +1830,14 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr"/>
@@ -1959,16 +1852,14 @@
         </is>
       </c>
       <c r="D48" s="13" t="n"/>
-      <c r="E48" s="13" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="15" t="n"/>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="15" t="n"/>
-      <c r="J48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr"/>
@@ -1983,16 +1874,14 @@
         </is>
       </c>
       <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="n"/>
+      <c r="G49" s="15" t="n"/>
       <c r="H49" s="15" t="n"/>
-      <c r="I49" s="15" t="n"/>
-      <c r="J49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr"/>
@@ -2007,16 +1896,14 @@
         </is>
       </c>
       <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="n"/>
+      <c r="G50" s="15" t="n"/>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="15" t="n"/>
-      <c r="J50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr"/>
@@ -2031,16 +1918,14 @@
         </is>
       </c>
       <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="15" t="n"/>
       <c r="H51" s="15" t="n"/>
-      <c r="I51" s="15" t="n"/>
-      <c r="J51" s="15" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
@@ -2066,16 +1951,14 @@
         </is>
       </c>
       <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="15" t="n"/>
       <c r="H53" s="15" t="n"/>
-      <c r="I53" s="15" t="n"/>
-      <c r="J53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr"/>
@@ -2090,16 +1973,14 @@
         </is>
       </c>
       <c r="D54" s="13" t="n"/>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="13" t="n"/>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="15" t="n"/>
       <c r="H54" s="15" t="n"/>
-      <c r="I54" s="15" t="n"/>
-      <c r="J54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr"/>
@@ -2114,16 +1995,14 @@
         </is>
       </c>
       <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
       <c r="H55" s="15" t="n"/>
-      <c r="I55" s="15" t="n"/>
-      <c r="J55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr"/>
@@ -2138,16 +2017,14 @@
         </is>
       </c>
       <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="n"/>
+      <c r="G56" s="15" t="n"/>
       <c r="H56" s="15" t="n"/>
-      <c r="I56" s="15" t="n"/>
-      <c r="J56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr"/>
@@ -2162,16 +2039,14 @@
         </is>
       </c>
       <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="n"/>
+      <c r="G57" s="15" t="n"/>
       <c r="H57" s="15" t="n"/>
-      <c r="I57" s="15" t="n"/>
-      <c r="J57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr"/>
@@ -2186,16 +2061,14 @@
         </is>
       </c>
       <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F58" s="15" t="n"/>
+      <c r="G58" s="15" t="n"/>
       <c r="H58" s="15" t="n"/>
-      <c r="I58" s="15" t="n"/>
-      <c r="J58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr"/>
@@ -2210,16 +2083,14 @@
         </is>
       </c>
       <c r="D59" s="13" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="13" t="n"/>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="n"/>
+      <c r="G59" s="15" t="n"/>
       <c r="H59" s="15" t="n"/>
-      <c r="I59" s="15" t="n"/>
-      <c r="J59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr"/>
@@ -2234,16 +2105,14 @@
         </is>
       </c>
       <c r="D60" s="13" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="13" t="n"/>
-      <c r="G60" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="n"/>
+      <c r="G60" s="15" t="n"/>
       <c r="H60" s="15" t="n"/>
-      <c r="I60" s="15" t="n"/>
-      <c r="J60" s="15" t="n"/>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
@@ -2269,16 +2138,14 @@
         </is>
       </c>
       <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="15" t="n"/>
       <c r="H62" s="15" t="n"/>
-      <c r="I62" s="15" t="n"/>
-      <c r="J62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr"/>
@@ -2293,16 +2160,14 @@
         </is>
       </c>
       <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="13" t="n"/>
-      <c r="G63" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="n"/>
+      <c r="G63" s="15" t="n"/>
       <c r="H63" s="15" t="n"/>
-      <c r="I63" s="15" t="n"/>
-      <c r="J63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr"/>
@@ -2317,16 +2182,14 @@
         </is>
       </c>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F64" s="15" t="n"/>
+      <c r="G64" s="15" t="n"/>
       <c r="H64" s="15" t="n"/>
-      <c r="I64" s="15" t="n"/>
-      <c r="J64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr"/>
@@ -2341,16 +2204,14 @@
         </is>
       </c>
       <c r="D65" s="13" t="n"/>
-      <c r="E65" s="13" t="n"/>
-      <c r="F65" s="13" t="n"/>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="n"/>
+      <c r="G65" s="15" t="n"/>
       <c r="H65" s="15" t="n"/>
-      <c r="I65" s="15" t="n"/>
-      <c r="J65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr"/>
@@ -2365,16 +2226,14 @@
         </is>
       </c>
       <c r="D66" s="13" t="n"/>
-      <c r="E66" s="13" t="n"/>
-      <c r="F66" s="13" t="n"/>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="n"/>
+      <c r="G66" s="15" t="n"/>
       <c r="H66" s="15" t="n"/>
-      <c r="I66" s="15" t="n"/>
-      <c r="J66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr"/>
@@ -2389,16 +2248,14 @@
         </is>
       </c>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
-      <c r="G67" s="16" t="inlineStr">
+      <c r="E67" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F67" s="15" t="n"/>
+      <c r="G67" s="15" t="n"/>
       <c r="H67" s="15" t="n"/>
-      <c r="I67" s="15" t="n"/>
-      <c r="J67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr"/>
@@ -2413,16 +2270,14 @@
         </is>
       </c>
       <c r="D68" s="13" t="n"/>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F68" s="15" t="n"/>
+      <c r="G68" s="15" t="n"/>
       <c r="H68" s="15" t="n"/>
-      <c r="I68" s="15" t="n"/>
-      <c r="J68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr"/>
@@ -2437,16 +2292,14 @@
         </is>
       </c>
       <c r="D69" s="13" t="n"/>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="n"/>
+      <c r="G69" s="15" t="n"/>
       <c r="H69" s="15" t="n"/>
-      <c r="I69" s="15" t="n"/>
-      <c r="J69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr"/>
@@ -2461,45 +2314,37 @@
         </is>
       </c>
       <c r="D70" s="13" t="n"/>
-      <c r="E70" s="13" t="n"/>
-      <c r="F70" s="13" t="n"/>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="n"/>
+      <c r="G70" s="15" t="n"/>
       <c r="H70" s="15" t="n"/>
-      <c r="I70" s="15" t="n"/>
-      <c r="J70" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A61:H61"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H34 H35 H36 H37 H38 H39 H40 H41 H42 H44 H45 H46 H47 H48 H49 H50 H51 H53 H54 H55 H56 H57 H59 H60 H62 H63 H65 H66 H68 H69 H70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F34 F35 F36 F37 F38 F39 F40 F41 F42 F44 F45 F46 F47 F48 F49 F50 F51 F53 F54 F55 F56 F57 F59 F60 F62 F63 F65 F66 F68 F69 F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="H58 H64 H67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F58 F64 F67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2513,19 +2358,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2560,35 +2403,25 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Also about</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Answer type</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">and </t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Answer type</t>
+          <t>Maturity Label</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Maturity Label</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -2618,16 +2451,14 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -2642,16 +2473,14 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -2666,16 +2495,14 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -2690,16 +2517,14 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -2714,16 +2539,14 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -2738,16 +2561,14 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -2762,16 +2583,14 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -2786,16 +2605,14 @@
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -2810,16 +2627,14 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -2845,16 +2660,14 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -2869,16 +2682,14 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -2893,16 +2704,14 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -2917,16 +2726,14 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -2941,16 +2748,14 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -2965,16 +2770,14 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -2989,16 +2792,14 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -3013,16 +2814,14 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -3037,16 +2836,14 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -3061,16 +2858,14 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -3085,16 +2880,14 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -3109,16 +2902,14 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -3144,16 +2935,14 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -3168,16 +2957,14 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -3192,16 +2979,14 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -3216,16 +3001,14 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -3240,16 +3023,14 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -3264,16 +3045,14 @@
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
       <c r="H33" s="15" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
@@ -3288,16 +3067,14 @@
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -3312,16 +3089,14 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -3336,16 +3111,14 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
@@ -3371,16 +3144,14 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -3395,16 +3166,14 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -3419,16 +3188,14 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
@@ -3454,16 +3221,14 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -3478,16 +3243,14 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -3502,16 +3265,14 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -3526,16 +3287,14 @@
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -3550,16 +3309,14 @@
         </is>
       </c>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -3574,44 +3331,36 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H29 H30 H31 H32 H33 H34 H36 H38 H39 H40 H42 H43 H44 H45 H46 H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F29 F30 F31 F32 F33 F34 F36 F38 F39 F40 F42 F43 F44 F45 F46 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="H28 H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F28 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3625,19 +3374,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3672,35 +3419,25 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Also about</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Answer type</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">and </t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Answer type</t>
+          <t>Maturity Label</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Maturity Label</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -3730,16 +3467,14 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -3754,16 +3489,14 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -3778,16 +3511,14 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -3802,16 +3533,14 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -3826,16 +3555,14 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -3850,16 +3577,14 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -3874,16 +3599,14 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr"/>
@@ -3898,16 +3621,14 @@
         </is>
       </c>
       <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr"/>
@@ -3922,16 +3643,14 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
@@ -3957,16 +3676,14 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -3981,16 +3698,14 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -4005,16 +3720,14 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -4029,16 +3742,14 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -4053,16 +3764,14 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -4077,16 +3786,14 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -4101,16 +3808,14 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -4125,16 +3830,14 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr"/>
@@ -4149,16 +3852,14 @@
         </is>
       </c>
       <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr"/>
@@ -4173,16 +3874,14 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -4208,16 +3907,14 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -4232,16 +3929,14 @@
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -4256,16 +3951,14 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -4280,16 +3973,14 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -4304,16 +3995,14 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr"/>
@@ -4328,16 +4017,14 @@
         </is>
       </c>
       <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr"/>
@@ -4352,16 +4039,14 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -4376,16 +4061,14 @@
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
       <c r="H33" s="15" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -4411,16 +4094,14 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -4435,16 +4116,14 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -4459,16 +4138,14 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
       <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -4483,16 +4160,14 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -4507,16 +4182,14 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr"/>
@@ -4531,16 +4204,14 @@
         </is>
       </c>
       <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr"/>
@@ -4555,16 +4226,14 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -4579,16 +4248,14 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -4603,16 +4270,14 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -4627,43 +4292,35 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H12 H13 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H26 H27 H28 H31 H32 H33 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F26 F27 F28 F31 F32 F33 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="H29 H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4677,19 +4334,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4724,35 +4379,25 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Also about</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Answer type</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">and </t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Answer type</t>
+          <t>Maturity Label</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Maturity Label</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Notes / Evidence</t>
         </is>
@@ -4782,16 +4427,14 @@
         </is>
       </c>
       <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
       <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr"/>
@@ -4806,16 +4449,14 @@
         </is>
       </c>
       <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr"/>
@@ -4830,16 +4471,14 @@
         </is>
       </c>
       <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
       <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr"/>
@@ -4854,16 +4493,14 @@
         </is>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr"/>
@@ -4878,16 +4515,14 @@
         </is>
       </c>
       <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr"/>
@@ -4902,16 +4537,14 @@
         </is>
       </c>
       <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr"/>
@@ -4926,16 +4559,14 @@
         </is>
       </c>
       <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
@@ -4961,16 +4592,14 @@
         </is>
       </c>
       <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr"/>
@@ -4985,16 +4614,14 @@
         </is>
       </c>
       <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr"/>
@@ -5009,16 +4636,14 @@
         </is>
       </c>
       <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr"/>
@@ -5033,16 +4658,14 @@
         </is>
       </c>
       <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr"/>
@@ -5057,16 +4680,14 @@
         </is>
       </c>
       <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr"/>
@@ -5081,16 +4702,14 @@
         </is>
       </c>
       <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr"/>
@@ -5105,16 +4724,14 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr"/>
@@ -5129,16 +4746,14 @@
         </is>
       </c>
       <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr"/>
@@ -5153,16 +4768,14 @@
         </is>
       </c>
       <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr"/>
@@ -5177,16 +4790,14 @@
         </is>
       </c>
       <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -5212,16 +4823,14 @@
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr"/>
@@ -5236,16 +4845,14 @@
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr"/>
@@ -5260,16 +4867,14 @@
         </is>
       </c>
       <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr"/>
@@ -5284,16 +4889,14 @@
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr"/>
@@ -5308,16 +4911,14 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr"/>
@@ -5332,16 +4933,14 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr"/>
@@ -5356,16 +4955,14 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
@@ -5391,16 +4988,14 @@
         </is>
       </c>
       <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr"/>
@@ -5415,16 +5010,14 @@
         </is>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
       <c r="H33" s="15" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr"/>
@@ -5439,16 +5032,14 @@
         </is>
       </c>
       <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr"/>
@@ -5463,16 +5054,14 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr"/>
@@ -5487,16 +5076,14 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr"/>
@@ -5511,16 +5098,14 @@
         </is>
       </c>
       <c r="D37" s="13" t="n"/>
-      <c r="E37" s="13" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
       <c r="H37" s="15" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr"/>
@@ -5535,16 +5120,14 @@
         </is>
       </c>
       <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr"/>
@@ -5559,16 +5142,14 @@
         </is>
       </c>
       <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="15" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
@@ -5594,16 +5175,14 @@
         </is>
       </c>
       <c r="D41" s="13" t="n"/>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr"/>
@@ -5618,16 +5197,14 @@
         </is>
       </c>
       <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr"/>
@@ -5642,16 +5219,14 @@
         </is>
       </c>
       <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr"/>
@@ -5666,16 +5241,14 @@
         </is>
       </c>
       <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr"/>
@@ -5690,16 +5263,14 @@
         </is>
       </c>
       <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
-      <c r="F45" s="13" t="n"/>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr"/>
@@ -5714,16 +5285,14 @@
         </is>
       </c>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr"/>
@@ -5738,44 +5307,36 @@
         </is>
       </c>
       <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>Scale 0-10</t>
-        </is>
-      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Scale 0-10</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="One subject this question is also about, beyond its own domain. Use the next column for a second. Leave them empty when there are none." type="list">
-      <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5 H6 H7 H8 H9 H10 H11 H13 H14 H15 H16 H17 H18 H20 H21 H22 H24 H25 H26 H27 H28 H29 H30 H32 H33 H34 H35 H37 H38 H39 H41 H42 H43 H44 H45 H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F32 F33 F34 F35 F37 F38 F39 F41 F42 F43 F44 F45 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="H19 H36 H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F19 F36 F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Deliverables/GC EA assessment tool - categories template.xlsx
+++ b/Deliverables/GC EA assessment tool - categories template.xlsx
@@ -2334,18 +2334,15 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A61:H61"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F34 F35 F36 F37 F38 F39 F40 F41 F42 F44 F45 F46 F47 F48 F49 F50 F51 F53 F54 F55 F56 F57 F59 F60 F62 F63 F65 F66 F68 F69 F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F58 F64 F67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
-      <formula1>"Yes,No,N/A"</formula1>
+    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+      <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3350,18 +3347,15 @@
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A27:H27"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F29 F30 F31 F32 F33 F34 F36 F38 F39 F40 F42 F43 F44 F45 F46 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F28 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
-      <formula1>"Yes,No,N/A"</formula1>
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+      <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4310,18 +4304,15 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F26 F27 F28 F31 F32 F33 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
-      <formula1>"Yes,No,N/A"</formula1>
+    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+      <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5326,18 +5317,15 @@
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F20 F21 F22 F24 F25 F26 F27 F28 F29 F30 F32 F33 F34 F35 F37 F38 F39 F41 F42 F43 F44 F45 F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Score" prompt="A maturity score from 0 to 10, or N/A when the question does not apply." type="list">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,N/A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F19 F36 F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Yes or no" prompt="Yes or no, or N/A when the question does not apply." type="list">
-      <formula1>"Yes,No,N/A"</formula1>
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+      <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Deliverables/GC EA assessment tool - categories template.xlsx
+++ b/Deliverables/GC EA assessment tool - categories template.xlsx
@@ -2335,13 +2335,13 @@
     <mergeCell ref="A61:H61"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
+    <dataValidation sqref="D4:D70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F4:F70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3348,13 +3348,13 @@
     <mergeCell ref="A27:H27"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4305,13 +4305,13 @@
     <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
+    <dataValidation sqref="D4:D44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F4:F44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5318,13 +5318,13 @@
     <mergeCell ref="A40:H40"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
+    <dataValidation sqref="D4:D47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="What else is it about?" prompt="The subjects this question is also about, beyond its own domain. Tick as many as apply. Leave it empty when there are none." type="list">
       <formula1>"Security,Privacy,Financial,Accessibility,Official Languages"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
+    <dataValidation sqref="E4:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="Scale or yes-or-no?" prompt="How this question is answered. Ours, and provisional: change it if it reads wrong." type="list">
       <formula1>"Scale 0-10,Yes / No"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
+    <dataValidation sqref="F4:F47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" promptTitle="The answer" prompt="A maturity score from 0 to 10, or Yes or No for a question that reads as one, or N/A when the question does not apply." type="list">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Deliverables/GC EA assessment tool - categories template.xlsx
+++ b/Deliverables/GC EA assessment tool - categories template.xlsx
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -268,6 +268,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -945,7 +948,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",NOT(ISNUMBER(F5))),"",IFERROR(VLOOKUP(F5,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -967,7 +973,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",NOT(ISNUMBER(F6))),"",IFERROR(VLOOKUP(F6,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -989,7 +998,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",NOT(ISNUMBER(F7))),"",IFERROR(VLOOKUP(F7,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -1011,7 +1023,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",NOT(ISNUMBER(F8))),"",IFERROR(VLOOKUP(F8,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -1033,7 +1048,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",NOT(ISNUMBER(F9))),"",IFERROR(VLOOKUP(F9,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -1055,7 +1073,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",NOT(ISNUMBER(F10))),"",IFERROR(VLOOKUP(F10,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -1077,7 +1098,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",NOT(ISNUMBER(F11))),"",IFERROR(VLOOKUP(F11,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
@@ -1099,7 +1123,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="G12" s="16">
+        <f>IF(OR(F12="",NOT(ISNUMBER(F12))),"",IFERROR(VLOOKUP(F12,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
@@ -1121,7 +1148,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",NOT(ISNUMBER(F13))),"",IFERROR(VLOOKUP(F13,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H13" s="15" t="n"/>
     </row>
     <row r="14">
@@ -1143,7 +1173,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="G14" s="16">
+        <f>IF(OR(F14="",NOT(ISNUMBER(F14))),"",IFERROR(VLOOKUP(F14,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
@@ -1165,7 +1198,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",NOT(ISNUMBER(F15))),"",IFERROR(VLOOKUP(F15,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -1187,7 +1223,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",NOT(ISNUMBER(F16))),"",IFERROR(VLOOKUP(F16,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -1209,7 +1248,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",NOT(ISNUMBER(F17))),"",IFERROR(VLOOKUP(F17,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -1231,7 +1273,10 @@
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",NOT(ISNUMBER(F18))),"",IFERROR(VLOOKUP(F18,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
@@ -1264,7 +1309,10 @@
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",NOT(ISNUMBER(F20))),"",IFERROR(VLOOKUP(F20,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -1286,7 +1334,10 @@
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",NOT(ISNUMBER(F21))),"",IFERROR(VLOOKUP(F21,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -1308,7 +1359,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",NOT(ISNUMBER(F22))),"",IFERROR(VLOOKUP(F22,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
@@ -1330,7 +1384,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="G23" s="16">
+        <f>IF(OR(F23="",NOT(ISNUMBER(F23))),"",IFERROR(VLOOKUP(F23,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
@@ -1352,7 +1409,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",NOT(ISNUMBER(F24))),"",IFERROR(VLOOKUP(F24,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
@@ -1374,7 +1434,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="G25" s="16">
+        <f>IF(OR(F25="",NOT(ISNUMBER(F25))),"",IFERROR(VLOOKUP(F25,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
@@ -1396,7 +1459,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",NOT(ISNUMBER(F26))),"",IFERROR(VLOOKUP(F26,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
@@ -1418,7 +1484,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="G27" s="16">
+        <f>IF(OR(F27="",NOT(ISNUMBER(F27))),"",IFERROR(VLOOKUP(F27,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H27" s="15" t="n"/>
     </row>
     <row r="28">
@@ -1440,7 +1509,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",NOT(ISNUMBER(F28))),"",IFERROR(VLOOKUP(F28,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -1462,7 +1534,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",NOT(ISNUMBER(F29))),"",IFERROR(VLOOKUP(F29,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -1484,7 +1559,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",NOT(ISNUMBER(F30))),"",IFERROR(VLOOKUP(F30,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
@@ -1506,7 +1584,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="G31" s="16">
+        <f>IF(OR(F31="",NOT(ISNUMBER(F31))),"",IFERROR(VLOOKUP(F31,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
@@ -1528,7 +1609,10 @@
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",NOT(ISNUMBER(F32))),"",IFERROR(VLOOKUP(F32,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H32" s="15" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
@@ -1561,7 +1645,10 @@
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="G34" s="16">
+        <f>IF(OR(F34="",NOT(ISNUMBER(F34))),"",IFERROR(VLOOKUP(F34,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H34" s="15" t="n"/>
     </row>
     <row r="35">
@@ -1583,7 +1670,10 @@
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",NOT(ISNUMBER(F35))),"",IFERROR(VLOOKUP(F35,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -1605,7 +1695,10 @@
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",NOT(ISNUMBER(F36))),"",IFERROR(VLOOKUP(F36,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
@@ -1627,7 +1720,10 @@
         </is>
       </c>
       <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="G37" s="16">
+        <f>IF(OR(F37="",NOT(ISNUMBER(F37))),"",IFERROR(VLOOKUP(F37,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
@@ -1649,7 +1745,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",NOT(ISNUMBER(F38))),"",IFERROR(VLOOKUP(F38,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -1671,7 +1770,10 @@
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",NOT(ISNUMBER(F39))),"",IFERROR(VLOOKUP(F39,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
@@ -1693,7 +1795,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="G40" s="16">
+        <f>IF(OR(F40="",NOT(ISNUMBER(F40))),"",IFERROR(VLOOKUP(F40,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H40" s="15" t="n"/>
     </row>
     <row r="41">
@@ -1715,7 +1820,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="G41" s="16">
+        <f>IF(OR(F41="",NOT(ISNUMBER(F41))),"",IFERROR(VLOOKUP(F41,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H41" s="15" t="n"/>
     </row>
     <row r="42">
@@ -1737,7 +1845,10 @@
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",NOT(ISNUMBER(F42))),"",IFERROR(VLOOKUP(F42,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H42" s="15" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
@@ -1770,7 +1881,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",NOT(ISNUMBER(F44))),"",IFERROR(VLOOKUP(F44,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H44" s="15" t="n"/>
     </row>
     <row r="45">
@@ -1792,7 +1906,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="G45" s="16">
+        <f>IF(OR(F45="",NOT(ISNUMBER(F45))),"",IFERROR(VLOOKUP(F45,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H45" s="15" t="n"/>
     </row>
     <row r="46">
@@ -1814,7 +1931,10 @@
         </is>
       </c>
       <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="G46" s="16">
+        <f>IF(OR(F46="",NOT(ISNUMBER(F46))),"",IFERROR(VLOOKUP(F46,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H46" s="15" t="n"/>
     </row>
     <row r="47">
@@ -1836,7 +1956,10 @@
         </is>
       </c>
       <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="G47" s="16">
+        <f>IF(OR(F47="",NOT(ISNUMBER(F47))),"",IFERROR(VLOOKUP(F47,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H47" s="15" t="n"/>
     </row>
     <row r="48">
@@ -1858,7 +1981,10 @@
         </is>
       </c>
       <c r="F48" s="15" t="n"/>
-      <c r="G48" s="15" t="n"/>
+      <c r="G48" s="16">
+        <f>IF(OR(F48="",NOT(ISNUMBER(F48))),"",IFERROR(VLOOKUP(F48,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H48" s="15" t="n"/>
     </row>
     <row r="49">
@@ -1880,7 +2006,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
+      <c r="G49" s="16">
+        <f>IF(OR(F49="",NOT(ISNUMBER(F49))),"",IFERROR(VLOOKUP(F49,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H49" s="15" t="n"/>
     </row>
     <row r="50">
@@ -1902,7 +2031,10 @@
         </is>
       </c>
       <c r="F50" s="15" t="n"/>
-      <c r="G50" s="15" t="n"/>
+      <c r="G50" s="16">
+        <f>IF(OR(F50="",NOT(ISNUMBER(F50))),"",IFERROR(VLOOKUP(F50,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H50" s="15" t="n"/>
     </row>
     <row r="51">
@@ -1924,7 +2056,10 @@
         </is>
       </c>
       <c r="F51" s="15" t="n"/>
-      <c r="G51" s="15" t="n"/>
+      <c r="G51" s="16">
+        <f>IF(OR(F51="",NOT(ISNUMBER(F51))),"",IFERROR(VLOOKUP(F51,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H51" s="15" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1">
@@ -1957,7 +2092,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
+      <c r="G53" s="16">
+        <f>IF(OR(F53="",NOT(ISNUMBER(F53))),"",IFERROR(VLOOKUP(F53,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H53" s="15" t="n"/>
     </row>
     <row r="54">
@@ -1979,7 +2117,10 @@
         </is>
       </c>
       <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
+      <c r="G54" s="16">
+        <f>IF(OR(F54="",NOT(ISNUMBER(F54))),"",IFERROR(VLOOKUP(F54,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H54" s="15" t="n"/>
     </row>
     <row r="55">
@@ -2001,7 +2142,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n"/>
-      <c r="G55" s="15" t="n"/>
+      <c r="G55" s="16">
+        <f>IF(OR(F55="",NOT(ISNUMBER(F55))),"",IFERROR(VLOOKUP(F55,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H55" s="15" t="n"/>
     </row>
     <row r="56">
@@ -2023,7 +2167,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n"/>
-      <c r="G56" s="15" t="n"/>
+      <c r="G56" s="16">
+        <f>IF(OR(F56="",NOT(ISNUMBER(F56))),"",IFERROR(VLOOKUP(F56,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H56" s="15" t="n"/>
     </row>
     <row r="57">
@@ -2045,7 +2192,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n"/>
-      <c r="G57" s="15" t="n"/>
+      <c r="G57" s="16">
+        <f>IF(OR(F57="",NOT(ISNUMBER(F57))),"",IFERROR(VLOOKUP(F57,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H57" s="15" t="n"/>
     </row>
     <row r="58">
@@ -2061,13 +2211,16 @@
         </is>
       </c>
       <c r="D58" s="13" t="n"/>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F58" s="15" t="n"/>
-      <c r="G58" s="15" t="n"/>
+      <c r="G58" s="16">
+        <f>IF(OR(F58="",NOT(ISNUMBER(F58))),"",IFERROR(VLOOKUP(F58,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H58" s="15" t="n"/>
     </row>
     <row r="59">
@@ -2089,7 +2242,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n"/>
-      <c r="G59" s="15" t="n"/>
+      <c r="G59" s="16">
+        <f>IF(OR(F59="",NOT(ISNUMBER(F59))),"",IFERROR(VLOOKUP(F59,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H59" s="15" t="n"/>
     </row>
     <row r="60">
@@ -2111,7 +2267,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
+      <c r="G60" s="16">
+        <f>IF(OR(F60="",NOT(ISNUMBER(F60))),"",IFERROR(VLOOKUP(F60,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H60" s="15" t="n"/>
     </row>
     <row r="61" ht="24" customHeight="1">
@@ -2144,7 +2303,10 @@
         </is>
       </c>
       <c r="F62" s="15" t="n"/>
-      <c r="G62" s="15" t="n"/>
+      <c r="G62" s="16">
+        <f>IF(OR(F62="",NOT(ISNUMBER(F62))),"",IFERROR(VLOOKUP(F62,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H62" s="15" t="n"/>
     </row>
     <row r="63">
@@ -2166,7 +2328,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n"/>
-      <c r="G63" s="15" t="n"/>
+      <c r="G63" s="16">
+        <f>IF(OR(F63="",NOT(ISNUMBER(F63))),"",IFERROR(VLOOKUP(F63,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H63" s="15" t="n"/>
     </row>
     <row r="64">
@@ -2182,13 +2347,16 @@
         </is>
       </c>
       <c r="D64" s="13" t="n"/>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F64" s="15" t="n"/>
-      <c r="G64" s="15" t="n"/>
+      <c r="G64" s="16">
+        <f>IF(OR(F64="",NOT(ISNUMBER(F64))),"",IFERROR(VLOOKUP(F64,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H64" s="15" t="n"/>
     </row>
     <row r="65">
@@ -2210,7 +2378,10 @@
         </is>
       </c>
       <c r="F65" s="15" t="n"/>
-      <c r="G65" s="15" t="n"/>
+      <c r="G65" s="16">
+        <f>IF(OR(F65="",NOT(ISNUMBER(F65))),"",IFERROR(VLOOKUP(F65,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H65" s="15" t="n"/>
     </row>
     <row r="66">
@@ -2232,7 +2403,10 @@
         </is>
       </c>
       <c r="F66" s="15" t="n"/>
-      <c r="G66" s="15" t="n"/>
+      <c r="G66" s="16">
+        <f>IF(OR(F66="",NOT(ISNUMBER(F66))),"",IFERROR(VLOOKUP(F66,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H66" s="15" t="n"/>
     </row>
     <row r="67">
@@ -2248,13 +2422,16 @@
         </is>
       </c>
       <c r="D67" s="13" t="n"/>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F67" s="15" t="n"/>
-      <c r="G67" s="15" t="n"/>
+      <c r="G67" s="16">
+        <f>IF(OR(F67="",NOT(ISNUMBER(F67))),"",IFERROR(VLOOKUP(F67,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H67" s="15" t="n"/>
     </row>
     <row r="68">
@@ -2276,7 +2453,10 @@
         </is>
       </c>
       <c r="F68" s="15" t="n"/>
-      <c r="G68" s="15" t="n"/>
+      <c r="G68" s="16">
+        <f>IF(OR(F68="",NOT(ISNUMBER(F68))),"",IFERROR(VLOOKUP(F68,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H68" s="15" t="n"/>
     </row>
     <row r="69">
@@ -2298,7 +2478,10 @@
         </is>
       </c>
       <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
+      <c r="G69" s="16">
+        <f>IF(OR(F69="",NOT(ISNUMBER(F69))),"",IFERROR(VLOOKUP(F69,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H69" s="15" t="n"/>
     </row>
     <row r="70">
@@ -2320,7 +2503,10 @@
         </is>
       </c>
       <c r="F70" s="15" t="n"/>
-      <c r="G70" s="15" t="n"/>
+      <c r="G70" s="16">
+        <f>IF(OR(F70="",NOT(ISNUMBER(F70))),"",IFERROR(VLOOKUP(F70,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H70" s="15" t="n"/>
     </row>
   </sheetData>
@@ -2454,7 +2640,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",NOT(ISNUMBER(F5))),"",IFERROR(VLOOKUP(F5,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -2476,7 +2665,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",NOT(ISNUMBER(F6))),"",IFERROR(VLOOKUP(F6,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -2498,7 +2690,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",NOT(ISNUMBER(F7))),"",IFERROR(VLOOKUP(F7,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -2520,7 +2715,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",NOT(ISNUMBER(F8))),"",IFERROR(VLOOKUP(F8,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -2542,7 +2740,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",NOT(ISNUMBER(F9))),"",IFERROR(VLOOKUP(F9,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -2564,7 +2765,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",NOT(ISNUMBER(F10))),"",IFERROR(VLOOKUP(F10,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -2586,7 +2790,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",NOT(ISNUMBER(F11))),"",IFERROR(VLOOKUP(F11,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
@@ -2608,7 +2815,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="G12" s="16">
+        <f>IF(OR(F12="",NOT(ISNUMBER(F12))),"",IFERROR(VLOOKUP(F12,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
@@ -2630,7 +2840,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",NOT(ISNUMBER(F13))),"",IFERROR(VLOOKUP(F13,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
@@ -2663,7 +2876,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",NOT(ISNUMBER(F15))),"",IFERROR(VLOOKUP(F15,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -2685,7 +2901,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",NOT(ISNUMBER(F16))),"",IFERROR(VLOOKUP(F16,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -2707,7 +2926,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",NOT(ISNUMBER(F17))),"",IFERROR(VLOOKUP(F17,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -2729,7 +2951,10 @@
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",NOT(ISNUMBER(F18))),"",IFERROR(VLOOKUP(F18,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
@@ -2751,7 +2976,10 @@
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="16">
+        <f>IF(OR(F19="",NOT(ISNUMBER(F19))),"",IFERROR(VLOOKUP(F19,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
@@ -2773,7 +3001,10 @@
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",NOT(ISNUMBER(F20))),"",IFERROR(VLOOKUP(F20,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -2795,7 +3026,10 @@
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",NOT(ISNUMBER(F21))),"",IFERROR(VLOOKUP(F21,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -2817,7 +3051,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",NOT(ISNUMBER(F22))),"",IFERROR(VLOOKUP(F22,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
@@ -2839,7 +3076,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="G23" s="16">
+        <f>IF(OR(F23="",NOT(ISNUMBER(F23))),"",IFERROR(VLOOKUP(F23,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
@@ -2861,7 +3101,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",NOT(ISNUMBER(F24))),"",IFERROR(VLOOKUP(F24,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
@@ -2883,7 +3126,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="G25" s="16">
+        <f>IF(OR(F25="",NOT(ISNUMBER(F25))),"",IFERROR(VLOOKUP(F25,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
@@ -2905,7 +3151,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",NOT(ISNUMBER(F26))),"",IFERROR(VLOOKUP(F26,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H26" s="15" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
@@ -2932,13 +3181,16 @@
         </is>
       </c>
       <c r="D28" s="13" t="n"/>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",NOT(ISNUMBER(F28))),"",IFERROR(VLOOKUP(F28,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -2960,7 +3212,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",NOT(ISNUMBER(F29))),"",IFERROR(VLOOKUP(F29,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -2982,7 +3237,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",NOT(ISNUMBER(F30))),"",IFERROR(VLOOKUP(F30,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
@@ -3004,7 +3262,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="G31" s="16">
+        <f>IF(OR(F31="",NOT(ISNUMBER(F31))),"",IFERROR(VLOOKUP(F31,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
@@ -3026,7 +3287,10 @@
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",NOT(ISNUMBER(F32))),"",IFERROR(VLOOKUP(F32,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
@@ -3048,7 +3312,10 @@
         </is>
       </c>
       <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="G33" s="16">
+        <f>IF(OR(F33="",NOT(ISNUMBER(F33))),"",IFERROR(VLOOKUP(F33,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H33" s="15" t="n"/>
     </row>
     <row r="34">
@@ -3070,7 +3337,10 @@
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="G34" s="16">
+        <f>IF(OR(F34="",NOT(ISNUMBER(F34))),"",IFERROR(VLOOKUP(F34,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H34" s="15" t="n"/>
     </row>
     <row r="35">
@@ -3086,13 +3356,16 @@
         </is>
       </c>
       <c r="D35" s="13" t="n"/>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",NOT(ISNUMBER(F35))),"",IFERROR(VLOOKUP(F35,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -3114,7 +3387,10 @@
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",NOT(ISNUMBER(F36))),"",IFERROR(VLOOKUP(F36,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H36" s="15" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
@@ -3147,7 +3423,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",NOT(ISNUMBER(F38))),"",IFERROR(VLOOKUP(F38,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -3169,7 +3448,10 @@
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",NOT(ISNUMBER(F39))),"",IFERROR(VLOOKUP(F39,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
@@ -3191,7 +3473,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="G40" s="16">
+        <f>IF(OR(F40="",NOT(ISNUMBER(F40))),"",IFERROR(VLOOKUP(F40,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H40" s="15" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
@@ -3224,7 +3509,10 @@
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",NOT(ISNUMBER(F42))),"",IFERROR(VLOOKUP(F42,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
@@ -3246,7 +3534,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="G43" s="16">
+        <f>IF(OR(F43="",NOT(ISNUMBER(F43))),"",IFERROR(VLOOKUP(F43,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H43" s="15" t="n"/>
     </row>
     <row r="44">
@@ -3268,7 +3559,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",NOT(ISNUMBER(F44))),"",IFERROR(VLOOKUP(F44,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H44" s="15" t="n"/>
     </row>
     <row r="45">
@@ -3290,7 +3584,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="G45" s="16">
+        <f>IF(OR(F45="",NOT(ISNUMBER(F45))),"",IFERROR(VLOOKUP(F45,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H45" s="15" t="n"/>
     </row>
     <row r="46">
@@ -3312,7 +3609,10 @@
         </is>
       </c>
       <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="G46" s="16">
+        <f>IF(OR(F46="",NOT(ISNUMBER(F46))),"",IFERROR(VLOOKUP(F46,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H46" s="15" t="n"/>
     </row>
     <row r="47">
@@ -3334,7 +3634,10 @@
         </is>
       </c>
       <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="G47" s="16">
+        <f>IF(OR(F47="",NOT(ISNUMBER(F47))),"",IFERROR(VLOOKUP(F47,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H47" s="15" t="n"/>
     </row>
   </sheetData>
@@ -3467,7 +3770,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",NOT(ISNUMBER(F5))),"",IFERROR(VLOOKUP(F5,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -3489,7 +3795,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",NOT(ISNUMBER(F6))),"",IFERROR(VLOOKUP(F6,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -3511,7 +3820,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",NOT(ISNUMBER(F7))),"",IFERROR(VLOOKUP(F7,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -3533,7 +3845,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",NOT(ISNUMBER(F8))),"",IFERROR(VLOOKUP(F8,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -3555,7 +3870,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",NOT(ISNUMBER(F9))),"",IFERROR(VLOOKUP(F9,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -3577,7 +3895,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",NOT(ISNUMBER(F10))),"",IFERROR(VLOOKUP(F10,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -3599,7 +3920,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",NOT(ISNUMBER(F11))),"",IFERROR(VLOOKUP(F11,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
@@ -3621,7 +3945,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="G12" s="16">
+        <f>IF(OR(F12="",NOT(ISNUMBER(F12))),"",IFERROR(VLOOKUP(F12,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
@@ -3643,7 +3970,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",NOT(ISNUMBER(F13))),"",IFERROR(VLOOKUP(F13,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H13" s="15" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
@@ -3676,7 +4006,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",NOT(ISNUMBER(F15))),"",IFERROR(VLOOKUP(F15,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -3698,7 +4031,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",NOT(ISNUMBER(F16))),"",IFERROR(VLOOKUP(F16,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -3720,7 +4056,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",NOT(ISNUMBER(F17))),"",IFERROR(VLOOKUP(F17,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -3742,7 +4081,10 @@
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",NOT(ISNUMBER(F18))),"",IFERROR(VLOOKUP(F18,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
@@ -3764,7 +4106,10 @@
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="16">
+        <f>IF(OR(F19="",NOT(ISNUMBER(F19))),"",IFERROR(VLOOKUP(F19,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
@@ -3786,7 +4131,10 @@
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",NOT(ISNUMBER(F20))),"",IFERROR(VLOOKUP(F20,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -3808,7 +4156,10 @@
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",NOT(ISNUMBER(F21))),"",IFERROR(VLOOKUP(F21,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -3830,7 +4181,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",NOT(ISNUMBER(F22))),"",IFERROR(VLOOKUP(F22,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
@@ -3852,7 +4206,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="G23" s="16">
+        <f>IF(OR(F23="",NOT(ISNUMBER(F23))),"",IFERROR(VLOOKUP(F23,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
@@ -3874,7 +4231,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",NOT(ISNUMBER(F24))),"",IFERROR(VLOOKUP(F24,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H24" s="15" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
@@ -3907,7 +4267,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",NOT(ISNUMBER(F26))),"",IFERROR(VLOOKUP(F26,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
@@ -3929,7 +4292,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="G27" s="16">
+        <f>IF(OR(F27="",NOT(ISNUMBER(F27))),"",IFERROR(VLOOKUP(F27,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H27" s="15" t="n"/>
     </row>
     <row r="28">
@@ -3951,7 +4317,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",NOT(ISNUMBER(F28))),"",IFERROR(VLOOKUP(F28,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -3967,13 +4336,16 @@
         </is>
       </c>
       <c r="D29" s="13" t="n"/>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",NOT(ISNUMBER(F29))),"",IFERROR(VLOOKUP(F29,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -3989,13 +4361,16 @@
         </is>
       </c>
       <c r="D30" s="13" t="n"/>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",NOT(ISNUMBER(F30))),"",IFERROR(VLOOKUP(F30,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
@@ -4017,7 +4392,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="G31" s="16">
+        <f>IF(OR(F31="",NOT(ISNUMBER(F31))),"",IFERROR(VLOOKUP(F31,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
@@ -4039,7 +4417,10 @@
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",NOT(ISNUMBER(F32))),"",IFERROR(VLOOKUP(F32,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
@@ -4061,7 +4442,10 @@
         </is>
       </c>
       <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="G33" s="16">
+        <f>IF(OR(F33="",NOT(ISNUMBER(F33))),"",IFERROR(VLOOKUP(F33,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H33" s="15" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
@@ -4094,7 +4478,10 @@
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",NOT(ISNUMBER(F35))),"",IFERROR(VLOOKUP(F35,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -4116,7 +4503,10 @@
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",NOT(ISNUMBER(F36))),"",IFERROR(VLOOKUP(F36,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
@@ -4138,7 +4528,10 @@
         </is>
       </c>
       <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="G37" s="16">
+        <f>IF(OR(F37="",NOT(ISNUMBER(F37))),"",IFERROR(VLOOKUP(F37,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
@@ -4160,7 +4553,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",NOT(ISNUMBER(F38))),"",IFERROR(VLOOKUP(F38,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -4182,7 +4578,10 @@
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",NOT(ISNUMBER(F39))),"",IFERROR(VLOOKUP(F39,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
@@ -4204,7 +4603,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="G40" s="16">
+        <f>IF(OR(F40="",NOT(ISNUMBER(F40))),"",IFERROR(VLOOKUP(F40,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H40" s="15" t="n"/>
     </row>
     <row r="41">
@@ -4226,7 +4628,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="G41" s="16">
+        <f>IF(OR(F41="",NOT(ISNUMBER(F41))),"",IFERROR(VLOOKUP(F41,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H41" s="15" t="n"/>
     </row>
     <row r="42">
@@ -4248,7 +4653,10 @@
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",NOT(ISNUMBER(F42))),"",IFERROR(VLOOKUP(F42,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
@@ -4270,7 +4678,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="G43" s="16">
+        <f>IF(OR(F43="",NOT(ISNUMBER(F43))),"",IFERROR(VLOOKUP(F43,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H43" s="15" t="n"/>
     </row>
     <row r="44">
@@ -4292,7 +4703,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",NOT(ISNUMBER(F44))),"",IFERROR(VLOOKUP(F44,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H44" s="15" t="n"/>
     </row>
   </sheetData>
@@ -4424,7 +4838,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",NOT(ISNUMBER(F5))),"",IFERROR(VLOOKUP(F5,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
@@ -4446,7 +4863,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",NOT(ISNUMBER(F6))),"",IFERROR(VLOOKUP(F6,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
@@ -4468,7 +4888,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",NOT(ISNUMBER(F7))),"",IFERROR(VLOOKUP(F7,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
@@ -4490,7 +4913,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",NOT(ISNUMBER(F8))),"",IFERROR(VLOOKUP(F8,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
@@ -4512,7 +4938,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",NOT(ISNUMBER(F9))),"",IFERROR(VLOOKUP(F9,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
@@ -4534,7 +4963,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",NOT(ISNUMBER(F10))),"",IFERROR(VLOOKUP(F10,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
@@ -4556,7 +4988,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",NOT(ISNUMBER(F11))),"",IFERROR(VLOOKUP(F11,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H11" s="15" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
@@ -4589,7 +5024,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",NOT(ISNUMBER(F13))),"",IFERROR(VLOOKUP(F13,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H13" s="15" t="n"/>
     </row>
     <row r="14">
@@ -4611,7 +5049,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="G14" s="16">
+        <f>IF(OR(F14="",NOT(ISNUMBER(F14))),"",IFERROR(VLOOKUP(F14,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
@@ -4633,7 +5074,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",NOT(ISNUMBER(F15))),"",IFERROR(VLOOKUP(F15,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
@@ -4655,7 +5099,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",NOT(ISNUMBER(F16))),"",IFERROR(VLOOKUP(F16,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
@@ -4677,7 +5124,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",NOT(ISNUMBER(F17))),"",IFERROR(VLOOKUP(F17,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
@@ -4699,7 +5149,10 @@
         </is>
       </c>
       <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",NOT(ISNUMBER(F18))),"",IFERROR(VLOOKUP(F18,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
@@ -4715,13 +5168,16 @@
         </is>
       </c>
       <c r="D19" s="13" t="n"/>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="16">
+        <f>IF(OR(F19="",NOT(ISNUMBER(F19))),"",IFERROR(VLOOKUP(F19,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
@@ -4743,7 +5199,10 @@
         </is>
       </c>
       <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",NOT(ISNUMBER(F20))),"",IFERROR(VLOOKUP(F20,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
@@ -4765,7 +5224,10 @@
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",NOT(ISNUMBER(F21))),"",IFERROR(VLOOKUP(F21,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
@@ -4787,7 +5249,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",NOT(ISNUMBER(F22))),"",IFERROR(VLOOKUP(F22,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H22" s="15" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
@@ -4820,7 +5285,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",NOT(ISNUMBER(F24))),"",IFERROR(VLOOKUP(F24,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
@@ -4842,7 +5310,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="G25" s="16">
+        <f>IF(OR(F25="",NOT(ISNUMBER(F25))),"",IFERROR(VLOOKUP(F25,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
@@ -4864,7 +5335,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",NOT(ISNUMBER(F26))),"",IFERROR(VLOOKUP(F26,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
@@ -4886,7 +5360,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="G27" s="16">
+        <f>IF(OR(F27="",NOT(ISNUMBER(F27))),"",IFERROR(VLOOKUP(F27,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H27" s="15" t="n"/>
     </row>
     <row r="28">
@@ -4908,7 +5385,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",NOT(ISNUMBER(F28))),"",IFERROR(VLOOKUP(F28,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
@@ -4930,7 +5410,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",NOT(ISNUMBER(F29))),"",IFERROR(VLOOKUP(F29,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
@@ -4952,7 +5435,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",NOT(ISNUMBER(F30))),"",IFERROR(VLOOKUP(F30,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H30" s="15" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
@@ -4985,7 +5471,10 @@
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",NOT(ISNUMBER(F32))),"",IFERROR(VLOOKUP(F32,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
@@ -5007,7 +5496,10 @@
         </is>
       </c>
       <c r="F33" s="15" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="G33" s="16">
+        <f>IF(OR(F33="",NOT(ISNUMBER(F33))),"",IFERROR(VLOOKUP(F33,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H33" s="15" t="n"/>
     </row>
     <row r="34">
@@ -5029,7 +5521,10 @@
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="G34" s="16">
+        <f>IF(OR(F34="",NOT(ISNUMBER(F34))),"",IFERROR(VLOOKUP(F34,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H34" s="15" t="n"/>
     </row>
     <row r="35">
@@ -5051,7 +5546,10 @@
         </is>
       </c>
       <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",NOT(ISNUMBER(F35))),"",IFERROR(VLOOKUP(F35,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
@@ -5067,13 +5565,16 @@
         </is>
       </c>
       <c r="D36" s="13" t="n"/>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",NOT(ISNUMBER(F36))),"",IFERROR(VLOOKUP(F36,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
@@ -5095,7 +5596,10 @@
         </is>
       </c>
       <c r="F37" s="15" t="n"/>
-      <c r="G37" s="15" t="n"/>
+      <c r="G37" s="16">
+        <f>IF(OR(F37="",NOT(ISNUMBER(F37))),"",IFERROR(VLOOKUP(F37,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
@@ -5117,7 +5621,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-      <c r="G38" s="15" t="n"/>
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",NOT(ISNUMBER(F38))),"",IFERROR(VLOOKUP(F38,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
@@ -5139,7 +5646,10 @@
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",NOT(ISNUMBER(F39))),"",IFERROR(VLOOKUP(F39,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H39" s="15" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
@@ -5172,7 +5682,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n"/>
-      <c r="G41" s="15" t="n"/>
+      <c r="G41" s="16">
+        <f>IF(OR(F41="",NOT(ISNUMBER(F41))),"",IFERROR(VLOOKUP(F41,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H41" s="15" t="n"/>
     </row>
     <row r="42">
@@ -5194,7 +5707,10 @@
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",NOT(ISNUMBER(F42))),"",IFERROR(VLOOKUP(F42,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
@@ -5216,7 +5732,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n"/>
-      <c r="G43" s="15" t="n"/>
+      <c r="G43" s="16">
+        <f>IF(OR(F43="",NOT(ISNUMBER(F43))),"",IFERROR(VLOOKUP(F43,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H43" s="15" t="n"/>
     </row>
     <row r="44">
@@ -5238,7 +5757,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",NOT(ISNUMBER(F44))),"",IFERROR(VLOOKUP(F44,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H44" s="15" t="n"/>
     </row>
     <row r="45">
@@ -5260,7 +5782,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n"/>
-      <c r="G45" s="15" t="n"/>
+      <c r="G45" s="16">
+        <f>IF(OR(F45="",NOT(ISNUMBER(F45))),"",IFERROR(VLOOKUP(F45,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H45" s="15" t="n"/>
     </row>
     <row r="46">
@@ -5276,13 +5801,16 @@
         </is>
       </c>
       <c r="D46" s="13" t="n"/>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
       <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
+      <c r="G46" s="16">
+        <f>IF(OR(F46="",NOT(ISNUMBER(F46))),"",IFERROR(VLOOKUP(F46,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H46" s="15" t="n"/>
     </row>
     <row r="47">
@@ -5304,7 +5832,10 @@
         </is>
       </c>
       <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
+      <c r="G47" s="16">
+        <f>IF(OR(F47="",NOT(ISNUMBER(F47))),"",IFERROR(VLOOKUP(F47,'Assessment Scale'!$A$3:$C$13,3,FALSE),""))</f>
+        <v/>
+      </c>
       <c r="H47" s="15" t="n"/>
     </row>
   </sheetData>
@@ -5355,39 +5886,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Colour</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -5399,17 +5928,15 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Dark Red</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Critical Gaps</t>
         </is>
@@ -5421,17 +5948,15 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Fragmented</t>
         </is>
@@ -5443,17 +5968,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Emergent</t>
         </is>
@@ -5465,17 +5988,15 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Orange-Yellow</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Defined</t>
         </is>
@@ -5487,17 +6008,15 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Integrated</t>
         </is>
@@ -5509,17 +6028,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Yellow-Green</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Managed</t>
         </is>
@@ -5531,17 +6048,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="A10" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Scalable &amp; Secure</t>
         </is>
@@ -5553,17 +6068,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="A11" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Dark Green</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Agile/Extensible</t>
         </is>
@@ -5575,17 +6088,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>Predictive</t>
         </is>
@@ -5597,17 +6108,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="A13" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Purple</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Symbiotic</t>
         </is>
@@ -5649,14 +6158,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Scores below are automatically calculated from the four architecture worksheets. Enter scores on each tab to populate this dashboard.</t>
         </is>
       </c>
-      <c r="B2" s="29" t="n"/>
-      <c r="C2" s="29" t="n"/>
-      <c r="D2" s="29" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -5753,18 +6262,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>OVERALL GC EA MATURITY SCORE</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n"/>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>Awaiting input</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n"/>
+      <c r="D10" s="31" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -5847,7 +6356,7 @@
       <c r="D17" s="12" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>This tab is your own Summary Dashboard, reproduced so nothing is missing from this copy. It does not calculate here: this workbook is for the Categories columns, and the scoring happens in the tool.</t>
         </is>
